--- a/董事长例会/总经办周例会汇报内容8.11.xlsx
+++ b/董事长例会/总经办周例会汇报内容8.11.xlsx
@@ -5,11 +5,11 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Administrator\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mrseven\Desktop\总经办文档\董事长例会\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="11775"/>
+    <workbookView windowWidth="27950" windowHeight="14080"/>
   </bookViews>
   <sheets>
     <sheet name="总经办" sheetId="8" r:id="rId1"/>
@@ -2309,7 +2309,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="9525" y="536575"/>
-          <a:ext cx="946150" cy="428625"/>
+          <a:ext cx="866775" cy="428625"/>
         </a:xfrm>
         <a:prstGeom prst="line">
           <a:avLst/>
@@ -2627,20 +2627,20 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:V13"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="18"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5"/>
   <cols>
-    <col min="1" max="1" width="12.5416666666667" style="1" customWidth="1"/>
-    <col min="2" max="2" width="36.8166666666667" style="1" hidden="1" customWidth="1"/>
-    <col min="3" max="3" width="30.0916666666667" style="1" hidden="1" customWidth="1"/>
-    <col min="4" max="4" width="39.5416666666667" style="1" hidden="1" customWidth="1"/>
-    <col min="5" max="5" width="43.25" style="1" hidden="1" customWidth="1"/>
-    <col min="6" max="6" width="43.125" style="1" hidden="1" customWidth="1"/>
-    <col min="7" max="7" width="46.875" style="1" hidden="1" customWidth="1"/>
-    <col min="8" max="11" width="54.75" style="1" hidden="1" customWidth="1"/>
-    <col min="12" max="12" width="54.75" style="1" customWidth="1"/>
-    <col min="13" max="14" width="58.75" style="1" customWidth="1"/>
-    <col min="15" max="15" width="20.0916666666667" style="1" customWidth="1"/>
-    <col min="16" max="16" width="19.0916666666667" style="1" customWidth="1"/>
+    <col min="1" max="1" width="12.5454545454545" style="1" customWidth="1"/>
+    <col min="2" max="2" width="36.8181818181818" style="1" hidden="1" customWidth="1"/>
+    <col min="3" max="3" width="30.0909090909091" style="1" hidden="1" customWidth="1"/>
+    <col min="4" max="4" width="39.5454545454545" style="1" hidden="1" customWidth="1"/>
+    <col min="5" max="5" width="43.2545454545455" style="1" hidden="1" customWidth="1"/>
+    <col min="6" max="6" width="43.1272727272727" style="1" hidden="1" customWidth="1"/>
+    <col min="7" max="7" width="46.8727272727273" style="1" hidden="1" customWidth="1"/>
+    <col min="8" max="11" width="54.7545454545455" style="1" hidden="1" customWidth="1"/>
+    <col min="12" max="12" width="54.7545454545455" style="1" customWidth="1"/>
+    <col min="13" max="14" width="58.7545454545455" style="1" customWidth="1"/>
+    <col min="15" max="15" width="20.0909090909091" style="1" customWidth="1"/>
+    <col min="16" max="16" width="19.0909090909091" style="1" customWidth="1"/>
     <col min="17" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
@@ -3186,7 +3186,7 @@
       <c r="U11" s="14"/>
       <c r="V11"/>
     </row>
-    <row r="12" ht="18.75" spans="1:22">
+    <row r="12" ht="17.25" spans="1:22">
       <c r="C12" s="26"/>
       <c r="R12" s="15"/>
       <c r="S12" s="14"/>
